--- a/experiment_results/combined_sweep/rtt_bursts_S1_atk1pct_wu300000.xlsx
+++ b/experiment_results/combined_sweep/rtt_bursts_S1_atk1pct_wu300000.xlsx
@@ -476,22 +476,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>00:010.0</t>
+          <t>00:010.5</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>18.3</t>
+          <t>15.9</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -516,7 +516,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>221</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -533,27 +533,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>00:020.0</t>
+          <t>00:020.1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -563,7 +563,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>9.63</t>
+          <t>8.88</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -573,7 +573,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>42</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -595,22 +595,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>23.1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -620,7 +620,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>9.06</t>
+          <t>7.37</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -647,27 +647,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>00:040.1</t>
+          <t>00:040.4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -677,7 +677,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>57</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -709,22 +709,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -761,27 +761,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>01:000.3</t>
+          <t>01:000.0</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>18.3</t>
+          <t>15.4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -818,27 +818,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>01:009.5</t>
+          <t>01:009.7</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>15.4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -848,17 +848,17 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -875,27 +875,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>01:020.1</t>
+          <t>01:020.3</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -932,22 +932,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>01:029.9</t>
+          <t>01:030.2</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -962,12 +962,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>4.22</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -989,27 +989,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>01:039.8</t>
+          <t>01:039.7</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>16.2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1046,27 +1046,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>01:050.1</t>
+          <t>01:050.2</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>16.1</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
           <t>19.4</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>20.5</t>
-        </is>
-      </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1103,27 +1103,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>02:000.2</t>
+          <t>01:059.9</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>16.2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1160,27 +1160,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>02:010.2</t>
+          <t>02:010.0</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>15.8</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1190,17 +1190,17 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1217,17 +1217,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>02:020.3</t>
+          <t>02:020.4</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>4.24</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>43</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1274,27 +1274,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>02:029.9</t>
+          <t>02:029.7</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1331,27 +1331,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>02:039.8</t>
+          <t>02:040.0</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>15.9</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1393,22 +1393,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>16.2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1445,27 +1445,27 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>02:054.8</t>
+          <t>02:054.7</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1475,7 +1475,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">

--- a/experiment_results/combined_sweep/rtt_bursts_S1_atk1pct_wu300000.xlsx
+++ b/experiment_results/combined_sweep/rtt_bursts_S1_atk1pct_wu300000.xlsx
@@ -476,22 +476,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>00:010.5</t>
+          <t>00:009.8</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>15.9</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>19.3</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -516,12 +516,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -533,27 +533,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>00:020.1</t>
+          <t>00:019.8</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>18.6</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -563,7 +563,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>8.88</t>
+          <t>7.45</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -573,7 +573,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>38</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -590,22 +590,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>00:030.1</t>
+          <t>00:030.0</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>18.2</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>23.1</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -620,7 +620,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>7.37</t>
+          <t>6.88</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -647,27 +647,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>00:040.4</t>
+          <t>00:039.9</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -677,17 +677,17 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -709,22 +709,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>16.2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -761,27 +761,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>01:000.0</t>
+          <t>00:059.9</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>15.4</t>
+          <t>16.3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -791,17 +791,17 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -818,27 +818,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>01:009.7</t>
+          <t>01:010.1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>15.4</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -848,17 +848,17 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -885,17 +885,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>4.71</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>75</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -937,22 +937,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -989,27 +989,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>01:039.7</t>
+          <t>01:040.1</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>16.2</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1019,17 +1019,17 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>4.96</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1046,27 +1046,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>01:050.2</t>
+          <t>01:049.8</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>16.1</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1076,17 +1076,17 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1103,27 +1103,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>01:059.9</t>
+          <t>02:000.1</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>16.2</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>19.3</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1133,12 +1133,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1160,27 +1160,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>02:010.0</t>
+          <t>02:010.5</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>15.8</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>71</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1217,22 +1217,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>02:020.4</t>
+          <t>02:019.6</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>10.11</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1274,27 +1274,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>02:029.7</t>
+          <t>02:030.2</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1304,17 +1304,17 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>9.51</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1331,27 +1331,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>02:040.0</t>
+          <t>02:039.9</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>15.9</t>
+          <t>16.4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1393,22 +1393,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>16.2</t>
+          <t>15.6</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1445,27 +1445,27 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>02:054.7</t>
+          <t>02:055.0</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1475,7 +1475,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
